--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="R2606efef7ad94685"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="Rbc1317c6ff0f4c3b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1190,10 +1190,10 @@
         <x:v>99</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="45" customHeight="1">
+    <x:row r="105" ht="72" customHeight="1">
       <x:c r="A105"/>
       <x:c r="B105" s="4" t="str">
-        <x:v>Improve responsiveness and reliability when opening, scrolling, zooming and editing PDFs; measure performance on dense drawings and repair reproducible stalls or interaction failures.</x:v>
+        <x:v>Improve responsiveness and reliability when opening, scrolling, zooming and editing PDFs. Use multiple CPU cores safely for background rendering, retain reusable parsed pages, prioritise visible tiles and cancel obsolete work. Measure dense-drawing rendering speed and UI responsiveness without reducing image quality or allowing unbounded memory use.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="45" customHeight="1">

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="Rbc1317c6ff0f4c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="R6a96d17eefb04d33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -613,10 +613,10 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="56" customHeight="1">
+    <x:row r="6" ht="72" customHeight="1">
       <x:c r="A6" s="2"/>
       <x:c r="B6" s="3" t="str">
-        <x:v>Fix tool states that prevent cancellation or switching tools, including after placing a callout arrow. Abandon stale callout anchors and held toolset payloads when changing tools. A callout-switching defect was reproduced and repaired on 2026-09-12; the reported Escape-resistant lockup still needs a reproducing sequence (82, 110)</x:v>
+        <x:v>Fix tool states that prevent cancellation or switching tools, including after placing a callout arrow. Abandon stale callout anchors and held toolset payloads when changing tools. Callout switching, Escape swallowed by inline panel editors, and stale scene mouse grabs have reproduced fixes and Qt regression coverage. Confirmation against the original reported sequence remains pending (82, 110)</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="90">

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="R6a96d17eefb04d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="R93c14452591543e9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1190,10 +1190,10 @@
         <x:v>99</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="72" customHeight="1">
+    <x:row r="105" ht="90" customHeight="1">
       <x:c r="A105"/>
       <x:c r="B105" s="4" t="str">
-        <x:v>Improve responsiveness and reliability when opening, scrolling, zooming and editing PDFs. Use multiple CPU cores safely for background rendering, retain reusable parsed pages, prioritise visible tiles and cancel obsolete work. Measure dense-drawing rendering speed and UI responsiveness without reducing image quality or allowing unbounded memory use.</x:v>
+        <x:v>Make the application as fast and responsive as practical without compromising functionality, usability or visual quality. Profile opening, scrolling, zooming, snapping, editing and undo on demanding documents. Use multiple CPU cores safely for background PDF rendering, retain reusable parsed pages, prioritise visible tiles and cancel obsolete work. Remove redundant work, measure improvements and keep memory bounded.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="45" customHeight="1">

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="R93c14452591543e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="Rd77c7659314b4c28"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -340,7 +340,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="top"/>
@@ -353,6 +353,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1262,8 +1265,104 @@
         <x:v>(found during 2026-09-11 walkthrough) Section header/footer columns must remain readable and editable in the default dialog width; Insert PDF preview instructions must wrap within the preview.</x:v>
       </x:c>
     </x:row>
+    <x:row r="117" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A117" s="5"/>
+      <x:c r="B117" s="5" t="str">
+        <x:v>Exported PDFs must not introduce an opaque white page background that appears when taking a snapshot in Bluebeam. Verify actual PDF content and transparency in saved/exported output.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="15" hidden="0" customHeight="1">
+      <x:c r="A118" s="5"/>
+      <x:c r="B118" s="5" t="str">
+        <x:v>Two-point scale calibration must show only a temporary dashed guide with a consistent on-screen size, without dimension graphics or a permanent measurement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A119" s="5"/>
+      <x:c r="B119" s="5" t="str">
+        <x:v>Replace sliders with editable numeric controls and visible up/down buttons for opacity, font size, thickness and other numeric styles in both Properties and the style toolbar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="15" hidden="0" customHeight="1">
+      <x:c r="A120" s="5"/>
+      <x:c r="B120" s="5" t="str">
+        <x:v>Arrowheads must finish at a sharp point. Show visual arrowhead previews in line-end dropdowns and the style toolbar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A121" s="5"/>
+      <x:c r="B121" s="5" t="str">
+        <x:v>Title-block hyperlinks must work in exported PDFs opened in other viewers. Support selected paper size with a chosen quantity or fit option; clarify whether the quantity refers to pages or title blocks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A122" s="5"/>
+      <x:c r="B122" s="5" t="str">
+        <x:v>Changing view synchronization must apply across all windows and split views of the same document, without enabling it separately in each view. Repair zoom and cursor anchoring while Document sync is active.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="15" hidden="0" customHeight="1">
+      <x:c r="A123" s="5"/>
+      <x:c r="B123" s="5" t="str">
+        <x:v>Live polygon/segment curve edits must not clip when the preview extends beyond its previous bounds or viewport; update the preview throughout the gesture.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="15" hidden="0" customHeight="1">
+      <x:c r="A124" s="5"/>
+      <x:c r="B124" s="5" t="str">
+        <x:v>Snapshot outline defaults must persist and apply to subsequent snapshots.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="15" hidden="0" customHeight="1">
+      <x:c r="A125" s="5"/>
+      <x:c r="B125" s="5" t="str">
+        <x:v>Structural break lines must expose size and placement controls, including moving the break along its segment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="15" hidden="0" customHeight="1">
+      <x:c r="A126" s="5"/>
+      <x:c r="B126" s="5" t="str">
+        <x:v>Repair alignment snapping during second-point placement; guides and snapped geometry must remain stable and agree.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="15" hidden="0" customHeight="1">
+      <x:c r="A127" s="5"/>
+      <x:c r="B127" s="5" t="str">
+        <x:v>Repair snapping to PDF content, including endpoints and intersections.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="15" hidden="0" customHeight="1">
+      <x:c r="A128" s="5"/>
+      <x:c r="B128" s="5" t="str">
+        <x:v>Clarify the unfinished report “whiteout should”; retain existing Whiteout requirements pending the missing detail.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A129" s="5"/>
+      <x:c r="B129" s="5" t="str">
+        <x:v>Fix excessive window minimum width on Windows: a 1920-pixel display currently requests a 1941-pixel client width and triggers QWindowsWindow::setGeometry warnings. Controls must remain accessible at that display size.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A130" s="5"/>
+      <x:c r="B130" s="5" t="str">
+        <x:v>Run the full automated suite and a fresh visual mouse/keyboard walkthrough of existing features; compare Bluebeam terminology, colours, formatting and workflows. Record concrete issues and repair them.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A131" s="5"/>
+      <x:c r="B131" s="5" t="str">
+        <x:v>Audit every markup type: expose all applicable editable properties in Properties, and important colour, hatch, line-end, arrowhead, line-style, thickness and opacity controls in the style toolbar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="15" hidden="0" customHeight="1">
+      <x:c r="A132" s="5"/>
+      <x:c r="B132" s="5" t="str">
+        <x:v>Continue profiling and improving responsiveness without reducing rendering quality or functionality, including synchronized zoom, drawing previews and snapping.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:B116"/>
+  <x:autoFilter ref="A1:B132"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="Rd77c7659314b4c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task list" sheetId="1" r:id="Rdc96bbb66d1c4662"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1292,7 +1292,7 @@
     <x:row r="121" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A121" s="5"/>
       <x:c r="B121" s="5" t="str">
-        <x:v>Title-block hyperlinks must work in exported PDFs opened in other viewers. Support selected paper size with a chosen quantity or fit option; clarify whether the quantity refers to pages or title blocks.</x:v>
+        <x:v>Title-block hyperlinks must work in exported PDFs opened in other viewers. Support selected paper size with a chosen page quantity. The previously mentioned fit option was withdrawn 2026-09-18.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1316,7 +1316,7 @@
     <x:row r="125" ht="15" hidden="0" customHeight="1">
       <x:c r="A125" s="5"/>
       <x:c r="B125" s="5" t="str">
-        <x:v>Structural break lines must expose size and placement controls, including moving the break along its segment.</x:v>
+        <x:v>Structural break lines must expose independent width, height and placement controls, including clear drag handles for each and moving the break along its segment.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -1334,7 +1334,7 @@
     <x:row r="128" ht="15" hidden="0" customHeight="1">
       <x:c r="A128" s="5"/>
       <x:c r="B128" s="5" t="str">
-        <x:v>Clarify the unfinished report “whiteout should”; retain existing Whiteout requirements pending the missing detail.</x:v>
+        <x:v>Whiteout removes only flattened PDF linework in the selected region; live editable markups must remain untouched. Scanned linework is flattened page content.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="26.399999618530273" hidden="0" customHeight="1">

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -488,7 +488,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="75" customHeight="1"/>
+    <row r="19" ht="75" customHeight="1">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PDF linework on the page looks blurrier than a snapshot of the same lines pasted beside it until zoomed in. Page lines must look as sharp as the pasted snapshot at every zoom.</t>
+        </is>
+      </c>
+    </row>
     <row r="20" ht="30" customHeight="1"/>
     <row r="21" ht="45" customHeight="1"/>
     <row r="22" ht="30" customHeight="1"/>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -495,9 +495,27 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1"/>
-    <row r="21" ht="45" customHeight="1"/>
-    <row r="22" ht="30" customHeight="1"/>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A pasted snapshot shows stray repeated dots in the app that do not appear in other PDF editors. The app must draw it as the export does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>After placing a rectangle or ellipse no size dialog may pop up; the size bar while drawing is the only size entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hatch must stay sharp at any hatch scale and zoom: linework, not a tiled picture.</t>
+        </is>
+      </c>
+    </row>
     <row r="24" ht="90" customHeight="1"/>
     <row r="25" ht="45" customHeight="1"/>
     <row r="26" ht="45" customHeight="1"/>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,13 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>Hatch must stay sharp at any hatch scale and zoom: linework, not a tiled picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bluebeam tool set import must line up one to one with Bluebeam: verify Sketch Tools against btx/Document1.pdf, where Bluebeam placed the same tools.</t>
         </is>
       </c>
     </row>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -512,7 +512,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hatch must stay sharp at any hatch scale and zoom: linework, not a tiled picture.</t>
+          <t>Hatch must stay sharp at any hatch scale and zoom: linework, not a tiled picture. **(amended)** Hatch scale is effectively infinite in both directions, in both the style toolbar and Properties.</t>
         </is>
       </c>
     </row>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -523,15 +523,76 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="90" customHeight="1"/>
-    <row r="25" ht="45" customHeight="1"/>
-    <row r="26" ht="45" customHeight="1"/>
-    <row r="27" ht="30" customHeight="1"/>
-    <row r="28" ht="45" customHeight="1"/>
-    <row r="29" ht="30" customHeight="1"/>
-    <row r="30" ht="30" customHeight="1"/>
-    <row r="31" ht="30" customHeight="1"/>
-    <row r="32" ht="30" customHeight="1"/>
+    <row r="24" ht="90" customHeight="1">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A1: Keep fractional font sizes exact (10.87 pt stays 10.87 pt, not rounded to a whole pixel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A2: Draw stamp artwork (e.g. the Titleblock) as linework, not a picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B3: Viewports: different scales in different regions of one sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B6: Link tool: a region that jumps to a page, a view, a file or a web address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B8: A library of named hatches and line styles like Bluebeam's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C2: Search the PDF's own text and the markups' text across all pages, list every hit, and replace text in markups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C4: Crop pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C5: Extract or split pages into a new PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Markups list panel like Bluebeam's: columns for colour, line style, font and similar; filter and sort; select rows to change colour, style or delete several markups at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Panel rail buttons can move between the left and right side but cannot be reordered top to bottom by dragging. They must be.</t>
+        </is>
+      </c>
+    </row>
     <row r="36" ht="45" customHeight="1"/>
     <row r="37" ht="30" customHeight="1"/>
     <row r="38" ht="30" customHeight="1"/>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -593,9 +593,41 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="45" customHeight="1"/>
-    <row r="37" ht="30" customHeight="1"/>
-    <row r="38" ht="30" customHeight="1"/>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Markups list panel lives only at the bottom of the window, and is shown or hidden by dragging its edge up or down, exactly like Bluebeam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hatch must be drawn behind the markup's outline, not over it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Line style and hatch pickers must be big dropdowns where each pattern is easy to tell apart, with its name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The scroll wheel over a dropdown must not cycle through its values, anywhere: toolbar, Properties and every dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The Cloud+ (cloud callout) icon shows only a cloud; it must show a cloud with a callout. Add leader icons for adding an arrow leader and a cloud leader, not just an arrow or just a cloud.</t>
+        </is>
+      </c>
+    </row>
     <row r="39" ht="45" customHeight="1"/>
     <row r="40" ht="30" customHeight="1"/>
     <row r="43" ht="45" customHeight="1"/>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -628,10 +628,48 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="45" customHeight="1"/>
-    <row r="40" ht="30" customHeight="1"/>
-    <row r="43" ht="45" customHeight="1"/>
-    <row r="44" ht="75" customHeight="1"/>
+    <row r="39" ht="45" customHeight="1">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Add-leader menu icons must be the callout icons themselves (text box + leader + arrow for an arrow callout, text box + leader + cloud for a cloud callout), not just an arrow or just a cloud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A viewport's frame shows only while it has been clicked into; otherwise it is hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Page setup and scale panel that follows the current page: units, decimal places, scale, the viewports on the page (add, change, delete), page size and orientation (e.g. landscape), and separate X and Y scales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A Sketch Tools markup (e.g. section cut) placed in MarkForge and opened in another PDF editor does not look right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A cloud markup opened in another editor shows a drag box of the wrong size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Every markup type must export correctly to PDF and look and behave right in other editors.</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="90" customHeight="1"/>
     <row r="46" ht="60" customHeight="1"/>
     <row r="47" ht="60" customHeight="1"/>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -670,9 +670,27 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="90" customHeight="1"/>
-    <row r="46" ht="60" customHeight="1"/>
-    <row r="47" ht="60" customHeight="1"/>
+    <row r="45" ht="90" customHeight="1">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sketch Tools contain groups within groups. Import them as nested groups linked together the way Bluebeam does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Import of any Bluebeam tool set must be exactly one to one with Bluebeam; it currently is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Right-click an image: Replace image from clipboard or from file. The new picture keeps its own aspect ratio and is sized from the existing image, exactly like Word.</t>
+        </is>
+      </c>
+    </row>
     <row r="48" ht="45" customHeight="1"/>
     <row r="49" ht="30" customHeight="1"/>
     <row r="50" ht="90" customHeight="1"/>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -691,7 +691,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customHeight="1"/>
+    <row r="48" ht="45" customHeight="1">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fix the margin bugs and every other export issue found, for every markup type throughout the app: anything added in MarkForge must appear exactly the same in another editor.</t>
+        </is>
+      </c>
+    </row>
     <row r="49" ht="30" customHeight="1"/>
     <row r="50" ht="90" customHeight="1"/>
     <row r="51" ht="30" customHeight="1"/>

--- a/docs/tasklist.xlsx
+++ b/docs/tasklist.xlsx
@@ -350,7 +350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -698,11 +698,55 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1"/>
-    <row r="50" ht="90" customHeight="1"/>
-    <row r="51" ht="30" customHeight="1"/>
-    <row r="54" ht="30" customHeight="1"/>
-    <row r="55" ht="30" customHeight="1"/>
+    <row r="49" ht="30" customHeight="1">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Dragging a measurement into or out of a viewport changes its scale automatically: finished inside the viewport it uses the viewport's scale, otherwise the page's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Move and copy modifiers like Bluebeam: only copy if Ctrl is held before the drag starts; during a move, Ctrl turns snapping off and Shift locks the move to straight lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pages panel: Ctrl+C and Ctrl+V copy and paste pages; with a page on the clipboard, hovering shows an insertion bar where it will go, exactly like Bluebeam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cloud size property for clouds, and a spacing (scale) property for line types that scales dot and dash spacing; line thickness must not change the spacing (it currently does).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>The add-leader icons are still wrong; fix them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Adding a curve or control point with Shift+click or Ctrl+click must not happen when the item is dragged afterwards; that is a Shift-drag or Ctrl-drag instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Format painter must behave exactly like Bluebeam's.</t>
+        </is>
+      </c>
+    </row>
     <row r="57" ht="30" customHeight="1"/>
     <row r="58" ht="30" customHeight="1"/>
     <row r="59" ht="30" customHeight="1"/>
